--- a/Libro2.xlsx
+++ b/Libro2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milto\OneDrive\Escritorio\MADDI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milto\OneDrive\Escritorio\MADDI2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996C9CBA-077D-49FD-9B1B-3C1CCE54EEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F3AD2D-B437-4F98-B15A-BC19F58ED264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{763E9B65-1FBE-4561-ABE8-3BF4ED2C7FAC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="135">
   <si>
     <t>CODIGO</t>
   </si>
@@ -432,6 +432,15 @@
   </si>
   <si>
     <t>Sueja Crotina Brola</t>
+  </si>
+  <si>
+    <t>DIP COPETINERO FLOR</t>
+  </si>
+  <si>
+    <t>ELEFANTE 13CM</t>
+  </si>
+  <si>
+    <t>MANTEL</t>
   </si>
 </sst>
 </file>
@@ -803,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE7444A-AF48-4250-B378-FB61DB0EB671}">
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -5185,6 +5194,18 @@
       <c r="F100">
         <v>1</v>
       </c>
+      <c r="H100">
+        <v>21</v>
+      </c>
+      <c r="I100">
+        <v>412</v>
+      </c>
+      <c r="J100">
+        <v>312</v>
+      </c>
+      <c r="K100">
+        <v>4112</v>
+      </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101">
@@ -5193,8 +5214,107 @@
       <c r="B101" t="s">
         <v>131</v>
       </c>
-      <c r="G101">
-        <v>20</v>
+      <c r="C101" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" t="s">
+        <v>128</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+      <c r="I101">
+        <v>1231</v>
+      </c>
+      <c r="J101">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>7790004701040</v>
+      </c>
+      <c r="B102" t="s">
+        <v>132</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" t="s">
+        <v>128</v>
+      </c>
+      <c r="F102">
+        <v>3</v>
+      </c>
+      <c r="I102">
+        <v>12314</v>
+      </c>
+      <c r="J102">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>7791234910071</v>
+      </c>
+      <c r="B103" t="s">
+        <v>133</v>
+      </c>
+      <c r="C103" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" t="s">
+        <v>3</v>
+      </c>
+      <c r="E103" t="s">
+        <v>128</v>
+      </c>
+      <c r="F103">
+        <v>4</v>
+      </c>
+      <c r="I103">
+        <v>12141</v>
+      </c>
+      <c r="J103">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>7790021125223</v>
+      </c>
+      <c r="B104" t="s">
+        <v>134</v>
+      </c>
+      <c r="C104" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" t="s">
+        <v>3</v>
+      </c>
+      <c r="E104" t="s">
+        <v>128</v>
+      </c>
+      <c r="F104">
+        <v>13</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>21</v>
+      </c>
+      <c r="I104">
+        <v>314153</v>
+      </c>
+      <c r="J104">
+        <v>4141341</v>
       </c>
     </row>
   </sheetData>
